--- a/data/predictions/Daanish.xlsx
+++ b/data/predictions/Daanish.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fb8ff3dc0463a38e/Documents/World Cup/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fb8ff3dc0463a38e/Documents/Personal Projects/World Cup/data/predictions/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DD650601-1036-430E-A916-E02C79251063}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{DD650601-1036-430E-A916-E02C79251063}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ABD23191-B1A5-42A5-AF03-0A6F3E6AB6E2}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{F4798D62-3F89-4340-A49F-A7EFFE42BF71}"/>
+    <workbookView xWindow="2295" yWindow="2295" windowWidth="21600" windowHeight="11295" xr2:uid="{F4798D62-3F89-4340-A49F-A7EFFE42BF71}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -660,7 +660,7 @@
   <dimension ref="A1:G73"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
